--- a/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-09.xlsx
+++ b/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-09.xlsx
@@ -474,751 +474,751 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>5583988609232</v>
+        <v>5583986529174</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Patricia</t>
+          <t>Valner</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Patricia Alves da Silva Leite</t>
+          <t>Valner dos Santos Franca</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>5583988310316</v>
+        <v>5583986248293</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Annelyne</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jose Araujo da Silva</t>
+          <t>Annelyne Soares Barbosa</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>5583996507445</v>
+        <v>5583993443192</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rebeca</t>
+          <t>Edson</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Rebeca Oliveira de Araujo</t>
+          <t>Edson Bruno Lourenco de Melo</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>5583987667410</v>
+        <v>5583988941535</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Felipe</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Felipe Ferreira Ernesto de Andrade</t>
+          <t>Casa Amarela Gas e Agua</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>5583999428565</v>
+        <v>5583988609232</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Valdemir</t>
+          <t>Patricia</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Valdemir Moureira Palitot</t>
+          <t>Patricia Alves da Silva Leite</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>5583988266856</v>
+        <v>5583988310316</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Henrique</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Henrique Leite Rodrigues</t>
+          <t>Jose Araujo da Silva</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>5583993752075</v>
+        <v>5583996507445</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Reboque</t>
+          <t>Rebeca</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Reboque Express</t>
+          <t>Rebeca Oliveira de Araujo</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>5584987135294</v>
+        <v>5583987667410</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Arnaldo</t>
+          <t>Felipe</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Arnaldo da Rocha</t>
+          <t>Felipe Ferreira Ernesto de Andrade</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>5583986642414</v>
+        <v>5583999428565</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Wesley</t>
+          <t>Valdemir</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wesley Teixeira Leite</t>
+          <t>Valdemir Moureira Palitot</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>5583988857319</v>
+        <v>5583988266856</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Henrique</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jose Brasilino da Silva</t>
+          <t>Henrique Leite Rodrigues</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>5583991027705</v>
+        <v>5583993752075</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Railton</t>
+          <t>Reboque</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Railton Miguel</t>
+          <t>Reboque Express</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>5584987052153</v>
+        <v>5584987135294</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Eliezer</t>
+          <t>Arnaldo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Eliezer Maximo</t>
+          <t>Arnaldo da Rocha</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>5583993350041</v>
+        <v>5519991082459</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Joao</t>
+          <t>Cell</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Joao Tavares dos Santos</t>
+          <t>Cell Project</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>5583988438992</v>
+        <v>5583986642414</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Martinho</t>
+          <t>Wesley</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Martinho Braz de Holanda</t>
+          <t>Wesley Teixeira Leite</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>5583991523179</v>
+        <v>5583988857319</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Maria das Gracas da Silva - Mana</t>
+          <t>Jose Brasilino da Silva</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>5583996972904</v>
+        <v>5583991027705</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Emmannuela</t>
+          <t>Railton</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Emmannuela Lacerda da Cruz</t>
+          <t>Railton Miguel</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>5583991626565</v>
+        <v>5584987052153</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Florentino</t>
+          <t>Eliezer</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Florentino de Carvalho Neto</t>
+          <t>Eliezer Maximo</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>5583987923977</v>
+        <v>5583993350041</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Valdenir</t>
+          <t>Joao</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Valdenir Lima da Cruz</t>
+          <t>Joao Tavares dos Santos</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>5583986604653</v>
+        <v>5583988438992</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Iranildo</t>
+          <t>Martinho</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Iranildo da Silva Costa</t>
+          <t>Martinho Braz de Holanda</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="3">
       <c r="A21" s="4" t="n">
-        <v>5583999031938</v>
+        <v>5583991523179</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Genivaldo</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Genivaldo Soares Coelho</t>
+          <t>Maria das Gracas da Silva - Mana</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="3">
       <c r="A22" s="4" t="n">
-        <v>5583986440623</v>
+        <v>5583996972904</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Isabel</t>
+          <t>Emmannuela</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Isabel Brito de Lemos Ribeiro</t>
+          <t>Emmannuela Lacerda da Cruz</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="3">
       <c r="A23" s="4" t="n">
-        <v>5583996291252</v>
+        <v>5583991626565</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Arlene</t>
+          <t>Florentino</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Arlene Filomena de Azevedo Oliveira</t>
+          <t>Florentino de Carvalho Neto</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="3">
       <c r="A24" s="4" t="n">
-        <v>5583986653020</v>
+        <v>5583987923977</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Aldelange</t>
+          <t>Valdenir</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Aldelange de Ferreira Brasil</t>
+          <t>Valdenir Lima da Cruz</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="3">
       <c r="A25" s="4" t="n">
-        <v>5584921487262</v>
+        <v>5583986604653</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Jefferson</t>
+          <t>Iranildo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jefferson Pedro Fernandes da Silva</t>
+          <t>Iranildo da Silva Costa</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="3">
       <c r="A26" s="4" t="n">
-        <v>5583996587282</v>
+        <v>5583999031938</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Silvestre</t>
+          <t>Genivaldo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Silvestre Carlos da Silva</t>
+          <t>Genivaldo Soares Coelho</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="3">
       <c r="A27" s="4" t="n">
-        <v>5583999462717</v>
+        <v>5583986440623</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cesar</t>
+          <t>Isabel</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cesar Silva de Farias</t>
+          <t>Isabel Brito de Lemos Ribeiro</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="3">
       <c r="A28" s="4" t="n">
-        <v>5583991559162</v>
+        <v>5583996291252</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Edson</t>
+          <t>Arlene</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Edson Rogerio da Silva</t>
+          <t>Arlene Filomena de Azevedo Oliveira</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="3">
       <c r="A29" s="4" t="n">
-        <v>5583994449535</v>
+        <v>5583986653020</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Anderson</t>
+          <t>Aldelange</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Anderson do Nascimento Eulalio</t>
+          <t>Aldelange de Ferreira Brasil</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="3">
       <c r="A30" s="4" t="n">
-        <v>5561981835076</v>
+        <v>5584921487262</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Benilton</t>
+          <t>Jefferson</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Benilton Alves de Aguiar</t>
+          <t>Jefferson Pedro Fernandes da Silva</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="3">
       <c r="A31" s="4" t="n">
-        <v>5583986694561</v>
+        <v>5583996587282</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ivete</t>
+          <t>Silvestre</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ivete Guedes Montenegro</t>
+          <t>Silvestre Carlos da Silva</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="3">
       <c r="A32" s="4" t="n">
-        <v>5583999487374</v>
+        <v>5583999462717</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Karlos</t>
+          <t>Cesar</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Karlos Andre Gomes de Araujo</t>
+          <t>Cesar Silva de Farias</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="3">
       <c r="A33" s="4" t="n">
-        <v>5562981579962</v>
+        <v>5583991559162</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Adriana</t>
+          <t>Edson</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Adriana Pereira da Silva</t>
+          <t>Edson Rogerio da Silva</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="3">
       <c r="A34" s="4" t="n">
-        <v>5583991709019</v>
+        <v>5583994449535</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Eberth</t>
+          <t>Anderson</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Eberth de Lima Borba</t>
+          <t>Anderson do Nascimento Eulalio</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="3">
       <c r="A35" s="4" t="n">
-        <v>5583998799510</v>
+        <v>5561981835076</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Francibelle</t>
+          <t>Benilton</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Francibelle Carneiro Ferreira</t>
+          <t>Benilton Alves de Aguiar</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="3">
       <c r="A36" s="4" t="n">
-        <v>5583996405067</v>
+        <v>5583986694561</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Luana</t>
+          <t>Ivete</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Luana Priscila Lima da Cunha</t>
+          <t>Ivete Guedes Montenegro</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="3">
       <c r="A37" s="4" t="n">
-        <v>5511954867474</v>
+        <v>5583999487374</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Camilla</t>
+          <t>Karlos</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Camilla Pinho</t>
+          <t>Karlos Andre Gomes de Araujo</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="3">
       <c r="A38" s="4" t="n">
-        <v>5583981782442</v>
+        <v>5562981579962</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Julio</t>
+          <t>Adriana</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Julio Cesar Ferreira Ramos</t>
+          <t>Adriana Pereira da Silva</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="3">
       <c r="A39" s="4" t="n">
-        <v>5583981186029</v>
+        <v>5583991709019</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Eberth</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Wilson Lisboa</t>
+          <t>Eberth de Lima Borba</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="3">
       <c r="A40" s="4" t="n">
-        <v>5583986098781</v>
+        <v>5583998799510</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Francibelle</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jose Leonardo Oliveira Costa</t>
+          <t>Francibelle Carneiro Ferreira</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="3">
       <c r="A41" s="4" t="n">
-        <v>5583999768723</v>
+        <v>5583996405067</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Kayllane</t>
+          <t>Luana</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Kayllane Vitória</t>
+          <t>Luana Priscila Lima da Cunha</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="3">
       <c r="A42" s="4" t="n">
-        <v>5583998321052</v>
+        <v>5511954867474</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Henry</t>
+          <t>Camilla</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Henry Gonçalves Pereira</t>
+          <t>Camilla Pinho</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="3">
       <c r="A43" s="4" t="n">
-        <v>5583987870968</v>
+        <v>5583981782442</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ivair</t>
+          <t>Julio</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ivair Lucas</t>
+          <t>Julio Cesar Ferreira Ramos</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="3">
       <c r="A44" s="4" t="n">
-        <v>5583998860025</v>
+        <v>5583981186029</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Fabio</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Fabio Costa da Silveira</t>
+          <t>Wilson Lisboa</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="3">
       <c r="A45" s="4" t="n">
-        <v>5583988317116</v>
+        <v>5583986098781</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Thayrone</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Thayrone Cesar Lima Coutinho</t>
+          <t>Jose Leonardo Oliveira Costa</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="3">
       <c r="A46" s="4" t="n">
-        <v>5583991416131</v>
+        <v>5583999768723</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Kayllane</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Maria do Socorro de Souza Lima</t>
+          <t>Kayllane Vitória</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="3">
       <c r="A47" s="4" t="n">
-        <v>5583988037929</v>
+        <v>5583998321052</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Alisson</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Alisson Francisco Carvalho da Silva</t>
+          <t>Henry Gonçalves Pereira</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="3">
       <c r="A48" s="4" t="n">
-        <v>5583997247219</v>
+        <v>5583987870968</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ednaldo</t>
+          <t>Ivair</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ednaldo Quirino Meireles</t>
+          <t>Ivair Lucas</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="3">
       <c r="A49" s="4" t="n">
-        <v>5583998291227</v>
+        <v>5583998860025</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Cristiano</t>
+          <t>Fabio</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cristiano Santos da Silva</t>
+          <t>Fabio Costa da Silveira</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="3">
       <c r="A50" s="4" t="n">
-        <v>5583981982467</v>
+        <v>5583988317116</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Fundacao</t>
+          <t>Thayrone</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Fundacao Casulo</t>
+          <t>Thayrone Cesar Lima Coutinho</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="3">
       <c r="A51" s="4" t="n">
-        <v>5583988947368</v>
+        <v>5583991416131</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Joyce</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Joyce Conde Pereira</t>
+          <t>Maria do Socorro de Souza Lima</t>
         </is>
       </c>
     </row>
